--- a/src/lib/__fixtures__/import-sample.xlsx
+++ b/src/lib/__fixtures__/import-sample.xlsx
@@ -178,6 +178,7 @@
     <col min="7" max="7" width="30" customWidth="1"/>
     <col min="8" max="8" width="30" customWidth="1"/>
     <col min="9" max="9" width="30" customWidth="1"/>
+    <col min="10" max="10" width="8" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1">
